--- a/outputs/fifa_team_statistics/excel_por_categoria/Movement.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Movement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -600,35 +600,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>413</v>
+        <v>617</v>
       </c>
       <c r="E4" t="n">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F4" t="n">
-        <v>605</v>
+        <v>572</v>
       </c>
       <c r="G4" t="n">
-        <v>951</v>
+        <v>1028</v>
       </c>
       <c r="H4" t="n">
-        <v>704</v>
+        <v>804</v>
       </c>
       <c r="I4" t="n">
-        <v>1655</v>
+        <v>1832</v>
       </c>
       <c r="J4" t="n">
-        <v>375</v>
+        <v>519</v>
       </c>
       <c r="K4" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="L4" t="n">
-        <v>712</v>
+        <v>812</v>
       </c>
     </row>
     <row r="5">
@@ -642,35 +642,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="E5" t="n">
-        <v>701</v>
+        <v>637</v>
       </c>
       <c r="F5" t="n">
-        <v>504</v>
+        <v>605</v>
       </c>
       <c r="G5" t="n">
-        <v>867</v>
+        <v>951</v>
       </c>
       <c r="H5" t="n">
-        <v>732</v>
+        <v>704</v>
       </c>
       <c r="I5" t="n">
-        <v>1599</v>
+        <v>1655</v>
       </c>
       <c r="J5" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="L5" t="n">
-        <v>686</v>
+        <v>712</v>
       </c>
     </row>
     <row r="6">
@@ -684,35 +684,35 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>440</v>
+        <v>394</v>
       </c>
       <c r="E6" t="n">
-        <v>631</v>
+        <v>701</v>
       </c>
       <c r="F6" t="n">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="G6" t="n">
-        <v>849</v>
+        <v>867</v>
       </c>
       <c r="H6" t="n">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="I6" t="n">
-        <v>1591</v>
+        <v>1599</v>
       </c>
       <c r="J6" t="n">
-        <v>550</v>
+        <v>379</v>
       </c>
       <c r="K6" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
-        <v>942</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7">
@@ -726,35 +726,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>440</v>
       </c>
       <c r="E7" t="n">
-        <v>498</v>
+        <v>631</v>
       </c>
       <c r="F7" t="n">
-        <v>620</v>
+        <v>520</v>
       </c>
       <c r="G7" t="n">
-        <v>938</v>
+        <v>849</v>
       </c>
       <c r="H7" t="n">
-        <v>649</v>
+        <v>742</v>
       </c>
       <c r="I7" t="n">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="J7" t="n">
-        <v>460</v>
+        <v>550</v>
       </c>
       <c r="K7" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="L7" t="n">
-        <v>741</v>
+        <v>942</v>
       </c>
     </row>
     <row r="8">
@@ -768,35 +768,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>469</v>
       </c>
       <c r="E8" t="n">
-        <v>576</v>
+        <v>498</v>
       </c>
       <c r="F8" t="n">
-        <v>511</v>
+        <v>620</v>
       </c>
       <c r="G8" t="n">
-        <v>872</v>
+        <v>938</v>
       </c>
       <c r="H8" t="n">
-        <v>607</v>
+        <v>649</v>
       </c>
       <c r="I8" t="n">
-        <v>1479</v>
+        <v>1587</v>
       </c>
       <c r="J8" t="n">
-        <v>324</v>
+        <v>460</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="L8" t="n">
-        <v>574</v>
+        <v>741</v>
       </c>
     </row>
     <row r="9">
@@ -810,35 +810,35 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>596</v>
       </c>
       <c r="F9" t="n">
-        <v>558</v>
+        <v>474</v>
       </c>
       <c r="G9" t="n">
-        <v>810</v>
+        <v>836</v>
       </c>
       <c r="H9" t="n">
-        <v>610</v>
+        <v>677</v>
       </c>
       <c r="I9" t="n">
-        <v>1420</v>
+        <v>1513</v>
       </c>
       <c r="J9" t="n">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K9" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="L9" t="n">
-        <v>744</v>
+        <v>807</v>
       </c>
     </row>
     <row r="10">
@@ -852,35 +852,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>296</v>
+        <v>462</v>
       </c>
       <c r="E10" t="n">
-        <v>619</v>
+        <v>526</v>
       </c>
       <c r="F10" t="n">
-        <v>421</v>
+        <v>498</v>
       </c>
       <c r="G10" t="n">
-        <v>710</v>
+        <v>866</v>
       </c>
       <c r="H10" t="n">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="I10" t="n">
-        <v>1336</v>
+        <v>1486</v>
       </c>
       <c r="J10" t="n">
-        <v>413</v>
+        <v>460</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="L10" t="n">
-        <v>759</v>
+        <v>988</v>
       </c>
     </row>
     <row r="11">
@@ -894,35 +894,35 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>461</v>
+        <v>392</v>
       </c>
       <c r="E11" t="n">
-        <v>452</v>
+        <v>576</v>
       </c>
       <c r="F11" t="n">
-        <v>402</v>
+        <v>511</v>
       </c>
       <c r="G11" t="n">
-        <v>742</v>
+        <v>872</v>
       </c>
       <c r="H11" t="n">
-        <v>573</v>
+        <v>607</v>
       </c>
       <c r="I11" t="n">
-        <v>1315</v>
+        <v>1479</v>
       </c>
       <c r="J11" t="n">
-        <v>411</v>
+        <v>324</v>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
-        <v>599</v>
+        <v>574</v>
       </c>
     </row>
     <row r="12">
@@ -936,35 +936,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>368</v>
+        <v>413</v>
       </c>
       <c r="E12" t="n">
-        <v>520</v>
+        <v>449</v>
       </c>
       <c r="F12" t="n">
-        <v>420</v>
+        <v>558</v>
       </c>
       <c r="G12" t="n">
-        <v>615</v>
+        <v>810</v>
       </c>
       <c r="H12" t="n">
-        <v>693</v>
+        <v>610</v>
       </c>
       <c r="I12" t="n">
-        <v>1308</v>
+        <v>1420</v>
       </c>
       <c r="J12" t="n">
-        <v>318</v>
+        <v>448</v>
       </c>
       <c r="K12" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="L12" t="n">
-        <v>519</v>
+        <v>744</v>
       </c>
     </row>
     <row r="13">
@@ -974,39 +974,39 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E13" t="n">
-        <v>514</v>
+        <v>619</v>
       </c>
       <c r="F13" t="n">
-        <v>474</v>
+        <v>421</v>
       </c>
       <c r="G13" t="n">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="H13" t="n">
-        <v>609</v>
+        <v>626</v>
       </c>
       <c r="I13" t="n">
-        <v>1308</v>
+        <v>1336</v>
       </c>
       <c r="J13" t="n">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="K13" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
-        <v>713</v>
+        <v>759</v>
       </c>
     </row>
     <row r="14">
@@ -1020,35 +1020,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>458</v>
+        <v>368</v>
       </c>
       <c r="E14" t="n">
-        <v>442</v>
+        <v>520</v>
       </c>
       <c r="F14" t="n">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="G14" t="n">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="H14" t="n">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="I14" t="n">
-        <v>1297</v>
+        <v>1308</v>
       </c>
       <c r="J14" t="n">
-        <v>463</v>
+        <v>318</v>
       </c>
       <c r="K14" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
-        <v>715</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15">
@@ -1058,39 +1058,39 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="E15" t="n">
-        <v>542</v>
+        <v>514</v>
       </c>
       <c r="F15" t="n">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="G15" t="n">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="H15" t="n">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="I15" t="n">
-        <v>1285</v>
+        <v>1308</v>
       </c>
       <c r="J15" t="n">
-        <v>308</v>
+        <v>422</v>
       </c>
       <c r="K15" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L15" t="n">
-        <v>659</v>
+        <v>713</v>
       </c>
     </row>
     <row r="16">
@@ -1104,35 +1104,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>409</v>
+        <v>458</v>
       </c>
       <c r="E16" t="n">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="F16" t="n">
-        <v>438</v>
+        <v>397</v>
       </c>
       <c r="G16" t="n">
-        <v>681</v>
+        <v>631</v>
       </c>
       <c r="H16" t="n">
-        <v>594</v>
+        <v>666</v>
       </c>
       <c r="I16" t="n">
-        <v>1275</v>
+        <v>1297</v>
       </c>
       <c r="J16" t="n">
-        <v>378</v>
+        <v>463</v>
       </c>
       <c r="K16" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="L16" t="n">
-        <v>709</v>
+        <v>715</v>
       </c>
     </row>
     <row r="17">
@@ -1146,35 +1146,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Congo DR</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>342</v>
+        <v>260</v>
       </c>
       <c r="E17" t="n">
         <v>542</v>
       </c>
       <c r="F17" t="n">
-        <v>353</v>
+        <v>483</v>
       </c>
       <c r="G17" t="n">
-        <v>730</v>
+        <v>705</v>
       </c>
       <c r="H17" t="n">
-        <v>507</v>
+        <v>580</v>
       </c>
       <c r="I17" t="n">
-        <v>1237</v>
+        <v>1285</v>
       </c>
       <c r="J17" t="n">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="K17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L17" t="n">
-        <v>636</v>
+        <v>659</v>
       </c>
     </row>
     <row r="18">
@@ -1188,35 +1188,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="E18" t="n">
-        <v>496</v>
+        <v>428</v>
       </c>
       <c r="F18" t="n">
-        <v>396</v>
+        <v>438</v>
       </c>
       <c r="G18" t="n">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="H18" t="n">
-        <v>545</v>
+        <v>594</v>
       </c>
       <c r="I18" t="n">
-        <v>1232</v>
+        <v>1275</v>
       </c>
       <c r="J18" t="n">
-        <v>287</v>
+        <v>378</v>
       </c>
       <c r="K18" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L18" t="n">
-        <v>685</v>
+        <v>709</v>
       </c>
     </row>
     <row r="19">
@@ -1230,35 +1230,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="E19" t="n">
-        <v>458</v>
+        <v>542</v>
       </c>
       <c r="F19" t="n">
-        <v>395</v>
+        <v>353</v>
       </c>
       <c r="G19" t="n">
-        <v>669</v>
+        <v>730</v>
       </c>
       <c r="H19" t="n">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="I19" t="n">
-        <v>1212</v>
+        <v>1237</v>
       </c>
       <c r="J19" t="n">
-        <v>283</v>
+        <v>323</v>
       </c>
       <c r="K19" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="L19" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="20">
@@ -1272,35 +1272,35 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>382</v>
+        <v>340</v>
       </c>
       <c r="E20" t="n">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="F20" t="n">
-        <v>350</v>
+        <v>396</v>
       </c>
       <c r="G20" t="n">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="H20" t="n">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="I20" t="n">
-        <v>1210</v>
+        <v>1232</v>
       </c>
       <c r="J20" t="n">
-        <v>378</v>
+        <v>287</v>
       </c>
       <c r="K20" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="L20" t="n">
-        <v>590</v>
+        <v>685</v>
       </c>
     </row>
     <row r="21">
@@ -1314,35 +1314,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="E21" t="n">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="F21" t="n">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G21" t="n">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="H21" t="n">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="I21" t="n">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="J21" t="n">
-        <v>360</v>
+        <v>283</v>
       </c>
       <c r="K21" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="L21" t="n">
-        <v>650</v>
+        <v>634</v>
       </c>
     </row>
     <row r="22">
@@ -1356,35 +1356,35 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Korea Republic</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>267</v>
+        <v>382</v>
       </c>
       <c r="E22" t="n">
-        <v>427</v>
+        <v>478</v>
       </c>
       <c r="F22" t="n">
-        <v>507</v>
+        <v>350</v>
       </c>
       <c r="G22" t="n">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="H22" t="n">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="I22" t="n">
-        <v>1201</v>
+        <v>1210</v>
       </c>
       <c r="J22" t="n">
-        <v>274</v>
+        <v>378</v>
       </c>
       <c r="K22" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L22" t="n">
-        <v>678</v>
+        <v>590</v>
       </c>
     </row>
     <row r="23">
@@ -1398,35 +1398,35 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>409</v>
+        <v>267</v>
       </c>
       <c r="E23" t="n">
-        <v>376</v>
+        <v>427</v>
       </c>
       <c r="F23" t="n">
-        <v>410</v>
+        <v>507</v>
       </c>
       <c r="G23" t="n">
-        <v>713</v>
+        <v>657</v>
       </c>
       <c r="H23" t="n">
-        <v>482</v>
+        <v>544</v>
       </c>
       <c r="I23" t="n">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="J23" t="n">
-        <v>380</v>
+        <v>274</v>
       </c>
       <c r="K23" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L23" t="n">
-        <v>642</v>
+        <v>678</v>
       </c>
     </row>
     <row r="24">
@@ -1440,35 +1440,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="E24" t="n">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="F24" t="n">
-        <v>347</v>
+        <v>410</v>
       </c>
       <c r="G24" t="n">
-        <v>599</v>
+        <v>713</v>
       </c>
       <c r="H24" t="n">
-        <v>583</v>
+        <v>482</v>
       </c>
       <c r="I24" t="n">
-        <v>1182</v>
+        <v>1195</v>
       </c>
       <c r="J24" t="n">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="K24" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L24" t="n">
-        <v>586</v>
+        <v>642</v>
       </c>
     </row>
     <row r="25">
@@ -1482,35 +1482,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>326</v>
+        <v>436</v>
       </c>
       <c r="E25" t="n">
-        <v>480</v>
+        <v>399</v>
       </c>
       <c r="F25" t="n">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="G25" t="n">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="H25" t="n">
-        <v>523</v>
+        <v>583</v>
       </c>
       <c r="I25" t="n">
-        <v>1112</v>
+        <v>1182</v>
       </c>
       <c r="J25" t="n">
-        <v>424</v>
+        <v>311</v>
       </c>
       <c r="K25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L25" t="n">
-        <v>861</v>
+        <v>586</v>
       </c>
     </row>
     <row r="26">
@@ -1524,35 +1524,35 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="E26" t="n">
-        <v>387</v>
+        <v>480</v>
       </c>
       <c r="F26" t="n">
-        <v>438</v>
+        <v>306</v>
       </c>
       <c r="G26" t="n">
-        <v>537</v>
+        <v>589</v>
       </c>
       <c r="H26" t="n">
-        <v>558</v>
+        <v>523</v>
       </c>
       <c r="I26" t="n">
-        <v>1095</v>
+        <v>1112</v>
       </c>
       <c r="J26" t="n">
-        <v>312</v>
+        <v>424</v>
       </c>
       <c r="K26" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L26" t="n">
-        <v>518</v>
+        <v>861</v>
       </c>
     </row>
     <row r="27">
@@ -1566,35 +1566,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="E27" t="n">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="F27" t="n">
-        <v>353</v>
+        <v>438</v>
       </c>
       <c r="G27" t="n">
-        <v>628</v>
+        <v>537</v>
       </c>
       <c r="H27" t="n">
-        <v>438</v>
+        <v>558</v>
       </c>
       <c r="I27" t="n">
-        <v>1066</v>
+        <v>1095</v>
       </c>
       <c r="J27" t="n">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="K27" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L27" t="n">
-        <v>696</v>
+        <v>518</v>
       </c>
     </row>
     <row r="28">
@@ -1818,35 +1818,35 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="E33" t="n">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="F33" t="n">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="G33" t="n">
-        <v>549</v>
+        <v>497</v>
       </c>
       <c r="H33" t="n">
-        <v>426</v>
+        <v>489</v>
       </c>
       <c r="I33" t="n">
-        <v>975</v>
+        <v>986</v>
       </c>
       <c r="J33" t="n">
-        <v>301</v>
+        <v>257</v>
       </c>
       <c r="K33" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="L33" t="n">
-        <v>603</v>
+        <v>676</v>
       </c>
     </row>
     <row r="34">
@@ -1860,35 +1860,35 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="E34" t="n">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="F34" t="n">
-        <v>264</v>
+        <v>337</v>
       </c>
       <c r="G34" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H34" t="n">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="I34" t="n">
-        <v>955</v>
+        <v>975</v>
       </c>
       <c r="J34" t="n">
-        <v>172</v>
+        <v>301</v>
       </c>
       <c r="K34" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="L34" t="n">
-        <v>430</v>
+        <v>603</v>
       </c>
     </row>
     <row r="35">
@@ -1902,35 +1902,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>300</v>
       </c>
       <c r="E35" t="n">
-        <v>317</v>
+        <v>391</v>
       </c>
       <c r="F35" t="n">
-        <v>321</v>
+        <v>264</v>
       </c>
       <c r="G35" t="n">
-        <v>519</v>
+        <v>548</v>
       </c>
       <c r="H35" t="n">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="I35" t="n">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="J35" t="n">
-        <v>233</v>
+        <v>172</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L35" t="n">
-        <v>481</v>
+        <v>430</v>
       </c>
     </row>
     <row r="36">
@@ -1944,35 +1944,35 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="E36" t="n">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="F36" t="n">
-        <v>284</v>
+        <v>321</v>
       </c>
       <c r="G36" t="n">
-        <v>418</v>
+        <v>519</v>
       </c>
       <c r="H36" t="n">
-        <v>471</v>
+        <v>419</v>
       </c>
       <c r="I36" t="n">
-        <v>889</v>
+        <v>938</v>
       </c>
       <c r="J36" t="n">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="K36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L36" t="n">
-        <v>532</v>
+        <v>481</v>
       </c>
     </row>
     <row r="37">
@@ -1986,35 +1986,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="E37" t="n">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="F37" t="n">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="G37" t="n">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="H37" t="n">
-        <v>417</v>
+        <v>471</v>
       </c>
       <c r="I37" t="n">
-        <v>866</v>
+        <v>889</v>
       </c>
       <c r="J37" t="n">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="K37" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L37" t="n">
-        <v>485</v>
+        <v>532</v>
       </c>
     </row>
     <row r="38">
@@ -2028,35 +2028,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="E38" t="n">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="F38" t="n">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="G38" t="n">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="H38" t="n">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="I38" t="n">
-        <v>834</v>
+        <v>866</v>
       </c>
       <c r="J38" t="n">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="K38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L38" t="n">
-        <v>407</v>
+        <v>485</v>
       </c>
     </row>
     <row r="39">
@@ -2070,35 +2070,35 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="E39" t="n">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="F39" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G39" t="n">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="H39" t="n">
-        <v>345</v>
+        <v>405</v>
       </c>
       <c r="I39" t="n">
-        <v>801</v>
+        <v>834</v>
       </c>
       <c r="J39" t="n">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="K39" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L39" t="n">
-        <v>458</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40">
@@ -2112,35 +2112,35 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IR Iran</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="E40" t="n">
-        <v>264</v>
+        <v>382</v>
       </c>
       <c r="F40" t="n">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="G40" t="n">
-        <v>356</v>
+        <v>456</v>
       </c>
       <c r="H40" t="n">
-        <v>405</v>
+        <v>345</v>
       </c>
       <c r="I40" t="n">
-        <v>761</v>
+        <v>801</v>
       </c>
       <c r="J40" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="K40" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L40" t="n">
-        <v>446</v>
+        <v>458</v>
       </c>
     </row>
     <row r="41">
@@ -2154,35 +2154,35 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="E41" t="n">
-        <v>323</v>
+        <v>264</v>
       </c>
       <c r="F41" t="n">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="G41" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="H41" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="I41" t="n">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="J41" t="n">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="K41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L41" t="n">
-        <v>465</v>
+        <v>446</v>
       </c>
     </row>
     <row r="42">
@@ -2196,35 +2196,35 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="E42" t="n">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="F42" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G42" t="n">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="H42" t="n">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="I42" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="J42" t="n">
-        <v>245</v>
+        <v>186</v>
       </c>
       <c r="K42" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L42" t="n">
-        <v>439</v>
+        <v>465</v>
       </c>
     </row>
     <row r="43">
@@ -2238,35 +2238,35 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="E43" t="n">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="F43" t="n">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="G43" t="n">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="H43" t="n">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="I43" t="n">
-        <v>707</v>
+        <v>740</v>
       </c>
       <c r="J43" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K43" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L43" t="n">
-        <v>523</v>
+        <v>439</v>
       </c>
     </row>
     <row r="44">
@@ -2280,35 +2280,35 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="E44" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F44" t="n">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="G44" t="n">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="H44" t="n">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="I44" t="n">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="J44" t="n">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="K44" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L44" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="45">
@@ -2542,7 +2542,7 @@
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -2601,13 +2601,13 @@
         <v>24.47916666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>14.01972710957493</v>
+        <v>14.01669154415448</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>12.5</v>
+        <v>12.75</v>
       </c>
       <c r="G2" t="n">
         <v>24.5</v>
@@ -2629,25 +2629,25 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>313.8541666666667</v>
+        <v>323.75</v>
       </c>
       <c r="D3" t="n">
-        <v>96.31596707807277</v>
+        <v>105.6611404242103</v>
       </c>
       <c r="E3" t="n">
         <v>155</v>
       </c>
       <c r="F3" t="n">
-        <v>231.75</v>
+        <v>237.25</v>
       </c>
       <c r="G3" t="n">
         <v>300</v>
       </c>
       <c r="H3" t="n">
-        <v>392.5</v>
+        <v>409</v>
       </c>
       <c r="I3" t="n">
-        <v>528</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4">
@@ -2660,22 +2660,22 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>429.5</v>
+        <v>440.9583333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>118.4764991509448</v>
+        <v>123.0415875608875</v>
       </c>
       <c r="E4" t="n">
         <v>164</v>
       </c>
       <c r="F4" t="n">
-        <v>362</v>
+        <v>363.5</v>
       </c>
       <c r="G4" t="n">
-        <v>427</v>
+        <v>427.5</v>
       </c>
       <c r="H4" t="n">
-        <v>496.5</v>
+        <v>521.5</v>
       </c>
       <c r="I4" t="n">
         <v>701</v>
@@ -2691,22 +2691,22 @@
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>369.2291666666667</v>
+        <v>379.7291666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>135.3930825071212</v>
+        <v>138.7618102442798</v>
       </c>
       <c r="E5" t="n">
         <v>143</v>
       </c>
       <c r="F5" t="n">
-        <v>264</v>
+        <v>264.75</v>
       </c>
       <c r="G5" t="n">
         <v>353</v>
       </c>
       <c r="H5" t="n">
-        <v>438</v>
+        <v>476.25</v>
       </c>
       <c r="I5" t="n">
         <v>727</v>
@@ -2722,22 +2722,22 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>606.0833333333334</v>
+        <v>623.3125</v>
       </c>
       <c r="D6" t="n">
-        <v>193.0259417394387</v>
+        <v>204.7734769488034</v>
       </c>
       <c r="E6" t="n">
         <v>310</v>
       </c>
       <c r="F6" t="n">
-        <v>444</v>
+        <v>454.25</v>
       </c>
       <c r="G6" t="n">
         <v>613</v>
       </c>
       <c r="H6" t="n">
-        <v>706.25</v>
+        <v>717.25</v>
       </c>
       <c r="I6" t="n">
         <v>1050</v>
@@ -2753,22 +2753,22 @@
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>506.5</v>
+        <v>521.125</v>
       </c>
       <c r="D7" t="n">
-        <v>138.3550781849892</v>
+        <v>144.2069471870938</v>
       </c>
       <c r="E7" t="n">
         <v>267</v>
       </c>
       <c r="F7" t="n">
-        <v>406.5</v>
+        <v>414.5</v>
       </c>
       <c r="G7" t="n">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="H7" t="n">
-        <v>597.25</v>
+        <v>612.5</v>
       </c>
       <c r="I7" t="n">
         <v>809</v>
@@ -2784,22 +2784,22 @@
         <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1112.583333333333</v>
+        <v>1144.4375</v>
       </c>
       <c r="D8" t="n">
-        <v>323.3235539941003</v>
+        <v>341.3260066551463</v>
       </c>
       <c r="E8" t="n">
         <v>577</v>
       </c>
       <c r="F8" t="n">
-        <v>858</v>
+        <v>883.25</v>
       </c>
       <c r="G8" t="n">
-        <v>1103.5</v>
+        <v>1147</v>
       </c>
       <c r="H8" t="n">
-        <v>1299.75</v>
+        <v>1315</v>
       </c>
       <c r="I8" t="n">
         <v>1859</v>
@@ -2815,22 +2815,22 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>309.0208333333333</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>93.57247494523101</v>
+        <v>100.2989149513868</v>
       </c>
       <c r="E9" t="n">
         <v>146</v>
       </c>
       <c r="F9" t="n">
-        <v>232.25</v>
+        <v>239</v>
       </c>
       <c r="G9" t="n">
         <v>309.5</v>
       </c>
       <c r="H9" t="n">
-        <v>378.25</v>
+        <v>388.25</v>
       </c>
       <c r="I9" t="n">
         <v>550</v>
@@ -2846,10 +2846,10 @@
         <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>33.75</v>
+        <v>34.6875</v>
       </c>
       <c r="D10" t="n">
-        <v>14.81732740710556</v>
+        <v>15.66831230982769</v>
       </c>
       <c r="E10" t="n">
         <v>13</v>
@@ -2861,7 +2861,7 @@
         <v>32</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I10" t="n">
         <v>77</v>
@@ -2877,10 +2877,10 @@
         <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>597.8958333333334</v>
+        <v>614.8958333333334</v>
       </c>
       <c r="D11" t="n">
-        <v>140.2616460190441</v>
+        <v>155.7767414403025</v>
       </c>
       <c r="E11" t="n">
         <v>342</v>
@@ -2889,13 +2889,13 @@
         <v>509.75</v>
       </c>
       <c r="G11" t="n">
-        <v>588</v>
+        <v>596.5</v>
       </c>
       <c r="H11" t="n">
-        <v>688.5</v>
+        <v>712.25</v>
       </c>
       <c r="I11" t="n">
-        <v>943</v>
+        <v>988</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Movement.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Movement.xlsx
@@ -426,80 +426,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="27" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Offers In Behind</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Offers In Between</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Offers In Behind</t>
+          <t>Offers In Front</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Offers In Between</t>
+          <t>Offers Inside Team Shape</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Offers In Front</t>
+          <t>Offers Outside Team Shape</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Offers Inside Team Shape</t>
+          <t>Offers To Receive</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Offers Outside Team Shape</t>
+          <t>Receptions Between Midfield And Defensive Line</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Offers To Receive</t>
+          <t>Receptions In Behind</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Receptions Between Midfield And Defensive Line</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Receptions In Behind</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Receptions Under Pressure</t>
         </is>
@@ -508,2017 +496,1633 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
+        <v>340</v>
+      </c>
+      <c r="C2" t="n">
+        <v>496</v>
       </c>
       <c r="D2" t="n">
-        <v>492</v>
+        <v>396</v>
       </c>
       <c r="E2" t="n">
-        <v>640</v>
+        <v>687</v>
       </c>
       <c r="F2" t="n">
-        <v>727</v>
+        <v>545</v>
       </c>
       <c r="G2" t="n">
-        <v>1050</v>
+        <v>1232</v>
       </c>
       <c r="H2" t="n">
-        <v>809</v>
+        <v>287</v>
       </c>
       <c r="I2" t="n">
-        <v>1859</v>
+        <v>31</v>
       </c>
       <c r="J2" t="n">
-        <v>418</v>
-      </c>
-      <c r="K2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>816</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
+        <v>260</v>
+      </c>
+      <c r="C3" t="n">
+        <v>542</v>
       </c>
       <c r="D3" t="n">
-        <v>528</v>
+        <v>483</v>
       </c>
       <c r="E3" t="n">
-        <v>628</v>
+        <v>705</v>
       </c>
       <c r="F3" t="n">
-        <v>684</v>
+        <v>580</v>
       </c>
       <c r="G3" t="n">
-        <v>1041</v>
+        <v>1285</v>
       </c>
       <c r="H3" t="n">
-        <v>799</v>
+        <v>308</v>
       </c>
       <c r="I3" t="n">
-        <v>1840</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>440</v>
-      </c>
-      <c r="K3" t="n">
-        <v>48</v>
-      </c>
-      <c r="L3" t="n">
-        <v>943</v>
+        <v>659</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
+        <v>155</v>
+      </c>
+      <c r="C4" t="n">
+        <v>298</v>
       </c>
       <c r="D4" t="n">
-        <v>617</v>
+        <v>205</v>
       </c>
       <c r="E4" t="n">
-        <v>643</v>
+        <v>349</v>
       </c>
       <c r="F4" t="n">
-        <v>572</v>
+        <v>309</v>
       </c>
       <c r="G4" t="n">
-        <v>1028</v>
+        <v>658</v>
       </c>
       <c r="H4" t="n">
-        <v>804</v>
+        <v>241</v>
       </c>
       <c r="I4" t="n">
-        <v>1832</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>519</v>
-      </c>
-      <c r="K4" t="n">
-        <v>56</v>
-      </c>
-      <c r="L4" t="n">
-        <v>812</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+        <v>267</v>
+      </c>
+      <c r="C5" t="n">
+        <v>371</v>
       </c>
       <c r="D5" t="n">
-        <v>413</v>
+        <v>337</v>
       </c>
       <c r="E5" t="n">
-        <v>637</v>
+        <v>549</v>
       </c>
       <c r="F5" t="n">
-        <v>605</v>
+        <v>426</v>
       </c>
       <c r="G5" t="n">
-        <v>951</v>
+        <v>975</v>
       </c>
       <c r="H5" t="n">
-        <v>704</v>
+        <v>301</v>
       </c>
       <c r="I5" t="n">
-        <v>1655</v>
+        <v>43</v>
       </c>
       <c r="J5" t="n">
-        <v>375</v>
-      </c>
-      <c r="K5" t="n">
-        <v>47</v>
-      </c>
-      <c r="L5" t="n">
-        <v>712</v>
+        <v>603</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
+        <v>617</v>
+      </c>
+      <c r="C6" t="n">
+        <v>643</v>
       </c>
       <c r="D6" t="n">
-        <v>394</v>
+        <v>572</v>
       </c>
       <c r="E6" t="n">
-        <v>701</v>
+        <v>1028</v>
       </c>
       <c r="F6" t="n">
-        <v>504</v>
+        <v>804</v>
       </c>
       <c r="G6" t="n">
-        <v>867</v>
+        <v>1832</v>
       </c>
       <c r="H6" t="n">
-        <v>732</v>
+        <v>519</v>
       </c>
       <c r="I6" t="n">
-        <v>1599</v>
+        <v>56</v>
       </c>
       <c r="J6" t="n">
-        <v>379</v>
-      </c>
-      <c r="K6" t="n">
-        <v>32</v>
-      </c>
-      <c r="L6" t="n">
-        <v>686</v>
+        <v>812</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
+        <v>286</v>
+      </c>
+      <c r="C7" t="n">
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>440</v>
+        <v>344</v>
       </c>
       <c r="E7" t="n">
-        <v>631</v>
+        <v>497</v>
       </c>
       <c r="F7" t="n">
-        <v>520</v>
+        <v>489</v>
       </c>
       <c r="G7" t="n">
-        <v>849</v>
+        <v>986</v>
       </c>
       <c r="H7" t="n">
-        <v>742</v>
+        <v>257</v>
       </c>
       <c r="I7" t="n">
-        <v>1591</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
-        <v>550</v>
-      </c>
-      <c r="K7" t="n">
-        <v>45</v>
-      </c>
-      <c r="L7" t="n">
-        <v>942</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
+        <v>413</v>
+      </c>
+      <c r="C8" t="n">
+        <v>637</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>605</v>
       </c>
       <c r="E8" t="n">
-        <v>498</v>
+        <v>951</v>
       </c>
       <c r="F8" t="n">
-        <v>620</v>
+        <v>704</v>
       </c>
       <c r="G8" t="n">
-        <v>938</v>
+        <v>1655</v>
       </c>
       <c r="H8" t="n">
-        <v>649</v>
+        <v>375</v>
       </c>
       <c r="I8" t="n">
-        <v>1587</v>
+        <v>47</v>
       </c>
       <c r="J8" t="n">
-        <v>460</v>
-      </c>
-      <c r="K8" t="n">
-        <v>55</v>
-      </c>
-      <c r="L8" t="n">
-        <v>741</v>
+        <v>712</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
+        <v>223</v>
+      </c>
+      <c r="C9" t="n">
+        <v>379</v>
       </c>
       <c r="D9" t="n">
-        <v>443</v>
+        <v>264</v>
       </c>
       <c r="E9" t="n">
-        <v>596</v>
+        <v>449</v>
       </c>
       <c r="F9" t="n">
-        <v>474</v>
+        <v>417</v>
       </c>
       <c r="G9" t="n">
-        <v>836</v>
+        <v>866</v>
       </c>
       <c r="H9" t="n">
-        <v>677</v>
+        <v>204</v>
       </c>
       <c r="I9" t="n">
-        <v>1513</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>447</v>
-      </c>
-      <c r="K9" t="n">
-        <v>64</v>
-      </c>
-      <c r="L9" t="n">
-        <v>807</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
+        <v>458</v>
+      </c>
+      <c r="C10" t="n">
+        <v>442</v>
       </c>
       <c r="D10" t="n">
-        <v>462</v>
+        <v>397</v>
       </c>
       <c r="E10" t="n">
-        <v>526</v>
+        <v>631</v>
       </c>
       <c r="F10" t="n">
-        <v>498</v>
+        <v>666</v>
       </c>
       <c r="G10" t="n">
-        <v>866</v>
+        <v>1297</v>
       </c>
       <c r="H10" t="n">
-        <v>620</v>
+        <v>463</v>
       </c>
       <c r="I10" t="n">
-        <v>1486</v>
+        <v>60</v>
       </c>
       <c r="J10" t="n">
-        <v>460</v>
-      </c>
-      <c r="K10" t="n">
-        <v>54</v>
-      </c>
-      <c r="L10" t="n">
-        <v>988</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
+        <v>368</v>
+      </c>
+      <c r="C11" t="n">
+        <v>520</v>
       </c>
       <c r="D11" t="n">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="E11" t="n">
-        <v>576</v>
+        <v>615</v>
       </c>
       <c r="F11" t="n">
-        <v>511</v>
+        <v>693</v>
       </c>
       <c r="G11" t="n">
-        <v>872</v>
+        <v>1308</v>
       </c>
       <c r="H11" t="n">
-        <v>607</v>
+        <v>318</v>
       </c>
       <c r="I11" t="n">
-        <v>1479</v>
+        <v>33</v>
       </c>
       <c r="J11" t="n">
-        <v>324</v>
-      </c>
-      <c r="K11" t="n">
-        <v>33</v>
-      </c>
-      <c r="L11" t="n">
-        <v>574</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
+        <v>342</v>
+      </c>
+      <c r="C12" t="n">
+        <v>542</v>
       </c>
       <c r="D12" t="n">
-        <v>413</v>
+        <v>353</v>
       </c>
       <c r="E12" t="n">
-        <v>449</v>
+        <v>730</v>
       </c>
       <c r="F12" t="n">
-        <v>558</v>
+        <v>507</v>
       </c>
       <c r="G12" t="n">
-        <v>810</v>
+        <v>1237</v>
       </c>
       <c r="H12" t="n">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="I12" t="n">
-        <v>1420</v>
+        <v>22</v>
       </c>
       <c r="J12" t="n">
-        <v>448</v>
-      </c>
-      <c r="K12" t="n">
-        <v>69</v>
-      </c>
-      <c r="L12" t="n">
-        <v>744</v>
+        <v>636</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="C13" t="n">
+        <v>317</v>
       </c>
       <c r="D13" t="n">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="E13" t="n">
-        <v>619</v>
+        <v>519</v>
       </c>
       <c r="F13" t="n">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G13" t="n">
-        <v>710</v>
+        <v>938</v>
       </c>
       <c r="H13" t="n">
-        <v>626</v>
+        <v>233</v>
       </c>
       <c r="I13" t="n">
-        <v>1336</v>
+        <v>26</v>
       </c>
       <c r="J13" t="n">
-        <v>413</v>
-      </c>
-      <c r="K13" t="n">
-        <v>32</v>
-      </c>
-      <c r="L13" t="n">
-        <v>759</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
+        <v>189</v>
+      </c>
+      <c r="C14" t="n">
+        <v>289</v>
       </c>
       <c r="D14" t="n">
-        <v>368</v>
+        <v>143</v>
       </c>
       <c r="E14" t="n">
-        <v>520</v>
+        <v>346</v>
       </c>
       <c r="F14" t="n">
-        <v>420</v>
+        <v>275</v>
       </c>
       <c r="G14" t="n">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="H14" t="n">
-        <v>693</v>
+        <v>228</v>
       </c>
       <c r="I14" t="n">
-        <v>1308</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>318</v>
-      </c>
-      <c r="K14" t="n">
-        <v>33</v>
-      </c>
-      <c r="L14" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
+        <v>232</v>
+      </c>
+      <c r="C15" t="n">
+        <v>305</v>
       </c>
       <c r="D15" t="n">
-        <v>320</v>
+        <v>203</v>
       </c>
       <c r="E15" t="n">
-        <v>514</v>
+        <v>371</v>
       </c>
       <c r="F15" t="n">
-        <v>474</v>
+        <v>369</v>
       </c>
       <c r="G15" t="n">
-        <v>699</v>
+        <v>740</v>
       </c>
       <c r="H15" t="n">
-        <v>609</v>
+        <v>245</v>
       </c>
       <c r="I15" t="n">
-        <v>1308</v>
+        <v>19</v>
       </c>
       <c r="J15" t="n">
-        <v>422</v>
-      </c>
-      <c r="K15" t="n">
-        <v>39</v>
-      </c>
-      <c r="L15" t="n">
-        <v>713</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
+        <v>326</v>
+      </c>
+      <c r="C16" t="n">
+        <v>480</v>
       </c>
       <c r="D16" t="n">
-        <v>458</v>
+        <v>306</v>
       </c>
       <c r="E16" t="n">
-        <v>442</v>
+        <v>589</v>
       </c>
       <c r="F16" t="n">
-        <v>397</v>
+        <v>523</v>
       </c>
       <c r="G16" t="n">
-        <v>631</v>
+        <v>1112</v>
       </c>
       <c r="H16" t="n">
-        <v>666</v>
+        <v>424</v>
       </c>
       <c r="I16" t="n">
-        <v>1297</v>
+        <v>46</v>
       </c>
       <c r="J16" t="n">
-        <v>463</v>
-      </c>
-      <c r="K16" t="n">
-        <v>60</v>
-      </c>
-      <c r="L16" t="n">
-        <v>715</v>
+        <v>861</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
+        <v>320</v>
+      </c>
+      <c r="C17" t="n">
+        <v>514</v>
       </c>
       <c r="D17" t="n">
-        <v>260</v>
+        <v>474</v>
       </c>
       <c r="E17" t="n">
-        <v>542</v>
+        <v>699</v>
       </c>
       <c r="F17" t="n">
-        <v>483</v>
+        <v>609</v>
       </c>
       <c r="G17" t="n">
-        <v>705</v>
+        <v>1308</v>
       </c>
       <c r="H17" t="n">
-        <v>580</v>
+        <v>422</v>
       </c>
       <c r="I17" t="n">
-        <v>1285</v>
+        <v>39</v>
       </c>
       <c r="J17" t="n">
-        <v>308</v>
-      </c>
-      <c r="K17" t="n">
-        <v>23</v>
-      </c>
-      <c r="L17" t="n">
-        <v>659</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
+        <v>270</v>
+      </c>
+      <c r="C18" t="n">
+        <v>387</v>
       </c>
       <c r="D18" t="n">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="E18" t="n">
-        <v>428</v>
+        <v>537</v>
       </c>
       <c r="F18" t="n">
-        <v>438</v>
+        <v>558</v>
       </c>
       <c r="G18" t="n">
-        <v>681</v>
+        <v>1095</v>
       </c>
       <c r="H18" t="n">
-        <v>594</v>
+        <v>312</v>
       </c>
       <c r="I18" t="n">
-        <v>1275</v>
+        <v>35</v>
       </c>
       <c r="J18" t="n">
-        <v>378</v>
-      </c>
-      <c r="K18" t="n">
-        <v>41</v>
-      </c>
-      <c r="L18" t="n">
-        <v>709</v>
+        <v>518</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Congo DR</t>
-        </is>
+        <v>492</v>
+      </c>
+      <c r="C19" t="n">
+        <v>640</v>
       </c>
       <c r="D19" t="n">
-        <v>342</v>
+        <v>727</v>
       </c>
       <c r="E19" t="n">
-        <v>542</v>
+        <v>1050</v>
       </c>
       <c r="F19" t="n">
-        <v>353</v>
+        <v>809</v>
       </c>
       <c r="G19" t="n">
-        <v>730</v>
+        <v>1859</v>
       </c>
       <c r="H19" t="n">
-        <v>507</v>
+        <v>418</v>
       </c>
       <c r="I19" t="n">
-        <v>1237</v>
+        <v>77</v>
       </c>
       <c r="J19" t="n">
-        <v>323</v>
-      </c>
-      <c r="K19" t="n">
-        <v>22</v>
-      </c>
-      <c r="L19" t="n">
-        <v>636</v>
+        <v>816</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
+        <v>413</v>
+      </c>
+      <c r="C20" t="n">
+        <v>449</v>
       </c>
       <c r="D20" t="n">
-        <v>340</v>
+        <v>558</v>
       </c>
       <c r="E20" t="n">
-        <v>496</v>
+        <v>810</v>
       </c>
       <c r="F20" t="n">
-        <v>396</v>
+        <v>610</v>
       </c>
       <c r="G20" t="n">
-        <v>687</v>
+        <v>1420</v>
       </c>
       <c r="H20" t="n">
-        <v>545</v>
+        <v>448</v>
       </c>
       <c r="I20" t="n">
-        <v>1232</v>
+        <v>69</v>
       </c>
       <c r="J20" t="n">
-        <v>287</v>
-      </c>
-      <c r="K20" t="n">
-        <v>31</v>
-      </c>
-      <c r="L20" t="n">
-        <v>685</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
+        <v>440</v>
+      </c>
+      <c r="C21" t="n">
+        <v>631</v>
       </c>
       <c r="D21" t="n">
-        <v>359</v>
+        <v>520</v>
       </c>
       <c r="E21" t="n">
-        <v>458</v>
+        <v>849</v>
       </c>
       <c r="F21" t="n">
-        <v>395</v>
+        <v>742</v>
       </c>
       <c r="G21" t="n">
-        <v>669</v>
+        <v>1591</v>
       </c>
       <c r="H21" t="n">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="I21" t="n">
-        <v>1212</v>
+        <v>45</v>
       </c>
       <c r="J21" t="n">
-        <v>283</v>
-      </c>
-      <c r="K21" t="n">
-        <v>29</v>
-      </c>
-      <c r="L21" t="n">
-        <v>634</v>
+        <v>942</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
+        <v>215</v>
+      </c>
+      <c r="C22" t="n">
+        <v>164</v>
       </c>
       <c r="D22" t="n">
-        <v>382</v>
+        <v>198</v>
       </c>
       <c r="E22" t="n">
-        <v>478</v>
+        <v>310</v>
       </c>
       <c r="F22" t="n">
-        <v>350</v>
+        <v>267</v>
       </c>
       <c r="G22" t="n">
-        <v>677</v>
+        <v>577</v>
       </c>
       <c r="H22" t="n">
-        <v>533</v>
+        <v>170</v>
       </c>
       <c r="I22" t="n">
-        <v>1210</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>378</v>
-      </c>
-      <c r="K22" t="n">
-        <v>47</v>
-      </c>
-      <c r="L22" t="n">
-        <v>590</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Korea Republic</t>
-        </is>
+        <v>252</v>
+      </c>
+      <c r="C23" t="n">
+        <v>350</v>
       </c>
       <c r="D23" t="n">
-        <v>267</v>
+        <v>232</v>
       </c>
       <c r="E23" t="n">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F23" t="n">
-        <v>507</v>
+        <v>405</v>
       </c>
       <c r="G23" t="n">
-        <v>657</v>
+        <v>834</v>
       </c>
       <c r="H23" t="n">
-        <v>544</v>
+        <v>212</v>
       </c>
       <c r="I23" t="n">
-        <v>1201</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>274</v>
-      </c>
-      <c r="K23" t="n">
-        <v>40</v>
-      </c>
-      <c r="L23" t="n">
-        <v>678</v>
+        <v>407</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
+        <v>227</v>
+      </c>
+      <c r="C24" t="n">
+        <v>264</v>
       </c>
       <c r="D24" t="n">
-        <v>409</v>
+        <v>270</v>
       </c>
       <c r="E24" t="n">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="F24" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G24" t="n">
-        <v>713</v>
+        <v>761</v>
       </c>
       <c r="H24" t="n">
-        <v>482</v>
+        <v>229</v>
       </c>
       <c r="I24" t="n">
-        <v>1195</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>380</v>
-      </c>
-      <c r="K24" t="n">
-        <v>47</v>
-      </c>
-      <c r="L24" t="n">
-        <v>642</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="C25" t="n">
+        <v>391</v>
       </c>
       <c r="D25" t="n">
-        <v>436</v>
+        <v>264</v>
       </c>
       <c r="E25" t="n">
-        <v>399</v>
+        <v>548</v>
       </c>
       <c r="F25" t="n">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="G25" t="n">
-        <v>599</v>
+        <v>955</v>
       </c>
       <c r="H25" t="n">
-        <v>583</v>
+        <v>172</v>
       </c>
       <c r="I25" t="n">
-        <v>1182</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>311</v>
-      </c>
-      <c r="K25" t="n">
-        <v>45</v>
-      </c>
-      <c r="L25" t="n">
-        <v>586</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
+        <v>392</v>
+      </c>
+      <c r="C26" t="n">
+        <v>576</v>
       </c>
       <c r="D26" t="n">
-        <v>326</v>
+        <v>511</v>
       </c>
       <c r="E26" t="n">
-        <v>480</v>
+        <v>872</v>
       </c>
       <c r="F26" t="n">
-        <v>306</v>
+        <v>607</v>
       </c>
       <c r="G26" t="n">
-        <v>589</v>
+        <v>1479</v>
       </c>
       <c r="H26" t="n">
-        <v>523</v>
+        <v>324</v>
       </c>
       <c r="I26" t="n">
-        <v>1112</v>
+        <v>33</v>
       </c>
       <c r="J26" t="n">
-        <v>424</v>
-      </c>
-      <c r="K26" t="n">
-        <v>46</v>
-      </c>
-      <c r="L26" t="n">
-        <v>861</v>
+        <v>574</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
+        <v>210</v>
+      </c>
+      <c r="C27" t="n">
+        <v>323</v>
       </c>
       <c r="D27" t="n">
-        <v>270</v>
+        <v>208</v>
       </c>
       <c r="E27" t="n">
-        <v>387</v>
+        <v>351</v>
       </c>
       <c r="F27" t="n">
-        <v>438</v>
+        <v>390</v>
       </c>
       <c r="G27" t="n">
-        <v>537</v>
+        <v>741</v>
       </c>
       <c r="H27" t="n">
-        <v>558</v>
+        <v>186</v>
       </c>
       <c r="I27" t="n">
-        <v>1095</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>312</v>
-      </c>
-      <c r="K27" t="n">
-        <v>35</v>
-      </c>
-      <c r="L27" t="n">
-        <v>518</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
+        <v>267</v>
+      </c>
+      <c r="C28" t="n">
+        <v>427</v>
       </c>
       <c r="D28" t="n">
-        <v>285</v>
+        <v>507</v>
       </c>
       <c r="E28" t="n">
-        <v>427</v>
+        <v>657</v>
       </c>
       <c r="F28" t="n">
-        <v>353</v>
+        <v>544</v>
       </c>
       <c r="G28" t="n">
-        <v>611</v>
+        <v>1201</v>
       </c>
       <c r="H28" t="n">
-        <v>454</v>
+        <v>274</v>
       </c>
       <c r="I28" t="n">
-        <v>1065</v>
+        <v>40</v>
       </c>
       <c r="J28" t="n">
-        <v>338</v>
-      </c>
-      <c r="K28" t="n">
-        <v>35</v>
-      </c>
-      <c r="L28" t="n">
-        <v>620</v>
+        <v>678</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
+        <v>394</v>
+      </c>
+      <c r="C29" t="n">
+        <v>701</v>
       </c>
       <c r="D29" t="n">
-        <v>337</v>
+        <v>504</v>
       </c>
       <c r="E29" t="n">
-        <v>407</v>
+        <v>867</v>
       </c>
       <c r="F29" t="n">
-        <v>319</v>
+        <v>732</v>
       </c>
       <c r="G29" t="n">
-        <v>629</v>
+        <v>1599</v>
       </c>
       <c r="H29" t="n">
-        <v>434</v>
+        <v>379</v>
       </c>
       <c r="I29" t="n">
-        <v>1063</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>317</v>
-      </c>
-      <c r="K29" t="n">
-        <v>46</v>
-      </c>
-      <c r="L29" t="n">
-        <v>562</v>
+        <v>686</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
+        <v>528</v>
+      </c>
+      <c r="C30" t="n">
+        <v>628</v>
       </c>
       <c r="D30" t="n">
-        <v>263</v>
+        <v>684</v>
       </c>
       <c r="E30" t="n">
-        <v>471</v>
+        <v>1041</v>
       </c>
       <c r="F30" t="n">
-        <v>328</v>
+        <v>799</v>
       </c>
       <c r="G30" t="n">
-        <v>559</v>
+        <v>1840</v>
       </c>
       <c r="H30" t="n">
-        <v>503</v>
+        <v>440</v>
       </c>
       <c r="I30" t="n">
-        <v>1062</v>
+        <v>48</v>
       </c>
       <c r="J30" t="n">
-        <v>267</v>
-      </c>
-      <c r="K30" t="n">
-        <v>14</v>
-      </c>
-      <c r="L30" t="n">
-        <v>563</v>
+        <v>943</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Scotland</t>
-        </is>
+        <v>409</v>
+      </c>
+      <c r="C31" t="n">
+        <v>376</v>
       </c>
       <c r="D31" t="n">
-        <v>231</v>
+        <v>410</v>
       </c>
       <c r="E31" t="n">
-        <v>400</v>
+        <v>713</v>
       </c>
       <c r="F31" t="n">
-        <v>409</v>
+        <v>482</v>
       </c>
       <c r="G31" t="n">
-        <v>558</v>
+        <v>1195</v>
       </c>
       <c r="H31" t="n">
-        <v>482</v>
+        <v>380</v>
       </c>
       <c r="I31" t="n">
-        <v>1040</v>
+        <v>47</v>
       </c>
       <c r="J31" t="n">
-        <v>230</v>
-      </c>
-      <c r="K31" t="n">
-        <v>15</v>
-      </c>
-      <c r="L31" t="n">
-        <v>430</v>
+        <v>642</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
+        <v>263</v>
+      </c>
+      <c r="C32" t="n">
+        <v>471</v>
       </c>
       <c r="D32" t="n">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="E32" t="n">
-        <v>448</v>
+        <v>559</v>
       </c>
       <c r="F32" t="n">
-        <v>265</v>
+        <v>503</v>
       </c>
       <c r="G32" t="n">
-        <v>547</v>
+        <v>1062</v>
       </c>
       <c r="H32" t="n">
-        <v>453</v>
+        <v>267</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="J32" t="n">
-        <v>196</v>
-      </c>
-      <c r="K32" t="n">
-        <v>18</v>
-      </c>
-      <c r="L32" t="n">
-        <v>405</v>
+        <v>563</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>296</v>
+      </c>
+      <c r="C33" t="n">
+        <v>619</v>
+      </c>
+      <c r="D33" t="n">
+        <v>421</v>
+      </c>
+      <c r="E33" t="n">
+        <v>710</v>
+      </c>
+      <c r="F33" t="n">
+        <v>626</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1336</v>
+      </c>
+      <c r="H33" t="n">
+        <v>413</v>
+      </c>
+      <c r="I33" t="n">
         <v>32</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>286</v>
-      </c>
-      <c r="E33" t="n">
-        <v>356</v>
-      </c>
-      <c r="F33" t="n">
-        <v>344</v>
-      </c>
-      <c r="G33" t="n">
-        <v>497</v>
-      </c>
-      <c r="H33" t="n">
-        <v>489</v>
-      </c>
-      <c r="I33" t="n">
-        <v>986</v>
-      </c>
       <c r="J33" t="n">
-        <v>257</v>
-      </c>
-      <c r="K33" t="n">
-        <v>22</v>
-      </c>
-      <c r="L33" t="n">
-        <v>676</v>
+        <v>759</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
+        <v>239</v>
+      </c>
+      <c r="C34" t="n">
+        <v>366</v>
       </c>
       <c r="D34" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="E34" t="n">
-        <v>371</v>
+        <v>418</v>
       </c>
       <c r="F34" t="n">
-        <v>337</v>
+        <v>471</v>
       </c>
       <c r="G34" t="n">
-        <v>549</v>
+        <v>889</v>
       </c>
       <c r="H34" t="n">
-        <v>426</v>
+        <v>248</v>
       </c>
       <c r="I34" t="n">
-        <v>975</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>301</v>
-      </c>
-      <c r="K34" t="n">
-        <v>43</v>
-      </c>
-      <c r="L34" t="n">
-        <v>603</v>
+        <v>532</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
+        <v>164</v>
+      </c>
+      <c r="C35" t="n">
+        <v>264</v>
       </c>
       <c r="D35" t="n">
-        <v>300</v>
+        <v>237</v>
       </c>
       <c r="E35" t="n">
-        <v>391</v>
+        <v>327</v>
       </c>
       <c r="F35" t="n">
-        <v>264</v>
+        <v>338</v>
       </c>
       <c r="G35" t="n">
-        <v>548</v>
+        <v>665</v>
       </c>
       <c r="H35" t="n">
-        <v>407</v>
+        <v>212</v>
       </c>
       <c r="I35" t="n">
-        <v>955</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>172</v>
-      </c>
-      <c r="K35" t="n">
-        <v>22</v>
-      </c>
-      <c r="L35" t="n">
-        <v>430</v>
+        <v>521</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
+        <v>382</v>
+      </c>
+      <c r="C36" t="n">
+        <v>478</v>
       </c>
       <c r="D36" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="E36" t="n">
-        <v>317</v>
+        <v>677</v>
       </c>
       <c r="F36" t="n">
-        <v>321</v>
+        <v>533</v>
       </c>
       <c r="G36" t="n">
-        <v>519</v>
+        <v>1210</v>
       </c>
       <c r="H36" t="n">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="I36" t="n">
-        <v>938</v>
+        <v>47</v>
       </c>
       <c r="J36" t="n">
-        <v>233</v>
-      </c>
-      <c r="K36" t="n">
-        <v>26</v>
-      </c>
-      <c r="L36" t="n">
-        <v>481</v>
+        <v>590</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>36</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
+        <v>169</v>
+      </c>
+      <c r="C37" t="n">
+        <v>285</v>
       </c>
       <c r="D37" t="n">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="E37" t="n">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="F37" t="n">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="G37" t="n">
-        <v>418</v>
+        <v>643</v>
       </c>
       <c r="H37" t="n">
-        <v>471</v>
+        <v>146</v>
       </c>
       <c r="I37" t="n">
-        <v>889</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>248</v>
-      </c>
-      <c r="K37" t="n">
-        <v>28</v>
-      </c>
-      <c r="L37" t="n">
-        <v>532</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Cabo Verde</t>
-        </is>
+        <v>207</v>
+      </c>
+      <c r="C38" t="n">
+        <v>276</v>
       </c>
       <c r="D38" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E38" t="n">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="F38" t="n">
-        <v>264</v>
+        <v>321</v>
       </c>
       <c r="G38" t="n">
-        <v>449</v>
+        <v>707</v>
       </c>
       <c r="H38" t="n">
-        <v>417</v>
+        <v>244</v>
       </c>
       <c r="I38" t="n">
-        <v>866</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>204</v>
-      </c>
-      <c r="K38" t="n">
-        <v>15</v>
-      </c>
-      <c r="L38" t="n">
-        <v>485</v>
+        <v>523</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
+        <v>231</v>
+      </c>
+      <c r="C39" t="n">
+        <v>400</v>
       </c>
       <c r="D39" t="n">
-        <v>252</v>
+        <v>409</v>
       </c>
       <c r="E39" t="n">
-        <v>350</v>
+        <v>558</v>
       </c>
       <c r="F39" t="n">
-        <v>232</v>
+        <v>482</v>
       </c>
       <c r="G39" t="n">
-        <v>429</v>
+        <v>1040</v>
       </c>
       <c r="H39" t="n">
-        <v>405</v>
+        <v>230</v>
       </c>
       <c r="I39" t="n">
-        <v>834</v>
+        <v>15</v>
       </c>
       <c r="J39" t="n">
-        <v>212</v>
-      </c>
-      <c r="K39" t="n">
-        <v>13</v>
-      </c>
-      <c r="L39" t="n">
-        <v>407</v>
+        <v>430</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>39</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
+        <v>462</v>
+      </c>
+      <c r="C40" t="n">
+        <v>526</v>
       </c>
       <c r="D40" t="n">
-        <v>197</v>
+        <v>498</v>
       </c>
       <c r="E40" t="n">
-        <v>382</v>
+        <v>866</v>
       </c>
       <c r="F40" t="n">
-        <v>222</v>
+        <v>620</v>
       </c>
       <c r="G40" t="n">
-        <v>456</v>
+        <v>1486</v>
       </c>
       <c r="H40" t="n">
-        <v>345</v>
+        <v>460</v>
       </c>
       <c r="I40" t="n">
-        <v>801</v>
+        <v>54</v>
       </c>
       <c r="J40" t="n">
-        <v>246</v>
-      </c>
-      <c r="K40" t="n">
-        <v>16</v>
-      </c>
-      <c r="L40" t="n">
-        <v>458</v>
+        <v>988</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>IR Iran</t>
-        </is>
+        <v>359</v>
+      </c>
+      <c r="C41" t="n">
+        <v>458</v>
       </c>
       <c r="D41" t="n">
-        <v>227</v>
+        <v>395</v>
       </c>
       <c r="E41" t="n">
-        <v>264</v>
+        <v>669</v>
       </c>
       <c r="F41" t="n">
-        <v>270</v>
+        <v>543</v>
       </c>
       <c r="G41" t="n">
-        <v>356</v>
+        <v>1212</v>
       </c>
       <c r="H41" t="n">
-        <v>405</v>
+        <v>283</v>
       </c>
       <c r="I41" t="n">
-        <v>761</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>229</v>
-      </c>
-      <c r="K41" t="n">
-        <v>28</v>
-      </c>
-      <c r="L41" t="n">
-        <v>446</v>
+        <v>634</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
+        <v>469</v>
+      </c>
+      <c r="C42" t="n">
+        <v>498</v>
       </c>
       <c r="D42" t="n">
-        <v>210</v>
+        <v>620</v>
       </c>
       <c r="E42" t="n">
-        <v>323</v>
+        <v>938</v>
       </c>
       <c r="F42" t="n">
-        <v>208</v>
+        <v>649</v>
       </c>
       <c r="G42" t="n">
-        <v>351</v>
+        <v>1587</v>
       </c>
       <c r="H42" t="n">
-        <v>390</v>
+        <v>460</v>
       </c>
       <c r="I42" t="n">
+        <v>55</v>
+      </c>
+      <c r="J42" t="n">
         <v>741</v>
-      </c>
-      <c r="J42" t="n">
-        <v>186</v>
-      </c>
-      <c r="K42" t="n">
-        <v>27</v>
-      </c>
-      <c r="L42" t="n">
-        <v>465</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
+        <v>285</v>
+      </c>
+      <c r="C43" t="n">
+        <v>427</v>
       </c>
       <c r="D43" t="n">
-        <v>232</v>
+        <v>353</v>
       </c>
       <c r="E43" t="n">
-        <v>305</v>
+        <v>611</v>
       </c>
       <c r="F43" t="n">
-        <v>203</v>
+        <v>454</v>
       </c>
       <c r="G43" t="n">
-        <v>371</v>
+        <v>1065</v>
       </c>
       <c r="H43" t="n">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="I43" t="n">
-        <v>740</v>
+        <v>35</v>
       </c>
       <c r="J43" t="n">
-        <v>245</v>
-      </c>
-      <c r="K43" t="n">
-        <v>19</v>
-      </c>
-      <c r="L43" t="n">
-        <v>439</v>
+        <v>620</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
+        <v>337</v>
+      </c>
+      <c r="C44" t="n">
+        <v>407</v>
       </c>
       <c r="D44" t="n">
-        <v>207</v>
+        <v>319</v>
       </c>
       <c r="E44" t="n">
-        <v>276</v>
+        <v>629</v>
       </c>
       <c r="F44" t="n">
-        <v>224</v>
+        <v>434</v>
       </c>
       <c r="G44" t="n">
-        <v>386</v>
+        <v>1063</v>
       </c>
       <c r="H44" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I44" t="n">
-        <v>707</v>
+        <v>46</v>
       </c>
       <c r="J44" t="n">
-        <v>244</v>
-      </c>
-      <c r="K44" t="n">
-        <v>24</v>
-      </c>
-      <c r="L44" t="n">
-        <v>523</v>
+        <v>562</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
+        <v>287</v>
+      </c>
+      <c r="C45" t="n">
+        <v>448</v>
       </c>
       <c r="D45" t="n">
-        <v>164</v>
+        <v>265</v>
       </c>
       <c r="E45" t="n">
-        <v>264</v>
+        <v>547</v>
       </c>
       <c r="F45" t="n">
-        <v>237</v>
+        <v>453</v>
       </c>
       <c r="G45" t="n">
-        <v>327</v>
+        <v>1000</v>
       </c>
       <c r="H45" t="n">
-        <v>338</v>
+        <v>196</v>
       </c>
       <c r="I45" t="n">
-        <v>665</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>212</v>
-      </c>
-      <c r="K45" t="n">
-        <v>18</v>
-      </c>
-      <c r="L45" t="n">
-        <v>521</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>45</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
+        <v>409</v>
+      </c>
+      <c r="C46" t="n">
+        <v>428</v>
       </c>
       <c r="D46" t="n">
-        <v>155</v>
+        <v>438</v>
       </c>
       <c r="E46" t="n">
-        <v>298</v>
+        <v>681</v>
       </c>
       <c r="F46" t="n">
-        <v>205</v>
+        <v>594</v>
       </c>
       <c r="G46" t="n">
-        <v>349</v>
+        <v>1275</v>
       </c>
       <c r="H46" t="n">
-        <v>309</v>
+        <v>378</v>
       </c>
       <c r="I46" t="n">
-        <v>658</v>
+        <v>41</v>
       </c>
       <c r="J46" t="n">
-        <v>241</v>
-      </c>
-      <c r="K46" t="n">
-        <v>24</v>
-      </c>
-      <c r="L46" t="n">
-        <v>573</v>
+        <v>709</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>46</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
+        <v>443</v>
+      </c>
+      <c r="C47" t="n">
+        <v>596</v>
       </c>
       <c r="D47" t="n">
-        <v>169</v>
+        <v>474</v>
       </c>
       <c r="E47" t="n">
-        <v>285</v>
+        <v>836</v>
       </c>
       <c r="F47" t="n">
-        <v>189</v>
+        <v>677</v>
       </c>
       <c r="G47" t="n">
-        <v>347</v>
+        <v>1513</v>
       </c>
       <c r="H47" t="n">
-        <v>296</v>
+        <v>447</v>
       </c>
       <c r="I47" t="n">
-        <v>643</v>
+        <v>64</v>
       </c>
       <c r="J47" t="n">
-        <v>146</v>
-      </c>
-      <c r="K47" t="n">
-        <v>22</v>
-      </c>
-      <c r="L47" t="n">
-        <v>361</v>
+        <v>807</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>47</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
+        <v>436</v>
+      </c>
+      <c r="C48" t="n">
+        <v>399</v>
       </c>
       <c r="D48" t="n">
-        <v>189</v>
+        <v>347</v>
       </c>
       <c r="E48" t="n">
-        <v>289</v>
+        <v>599</v>
       </c>
       <c r="F48" t="n">
-        <v>143</v>
+        <v>583</v>
       </c>
       <c r="G48" t="n">
-        <v>346</v>
+        <v>1182</v>
       </c>
       <c r="H48" t="n">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="I48" t="n">
-        <v>621</v>
+        <v>45</v>
       </c>
       <c r="J48" t="n">
-        <v>228</v>
-      </c>
-      <c r="K48" t="n">
-        <v>17</v>
-      </c>
-      <c r="L48" t="n">
-        <v>524</v>
+        <v>586</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
+        <v>197</v>
+      </c>
+      <c r="C49" t="n">
+        <v>382</v>
       </c>
       <c r="D49" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E49" t="n">
-        <v>164</v>
+        <v>456</v>
       </c>
       <c r="F49" t="n">
-        <v>198</v>
+        <v>345</v>
       </c>
       <c r="G49" t="n">
-        <v>310</v>
+        <v>801</v>
       </c>
       <c r="H49" t="n">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="I49" t="n">
-        <v>577</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>170</v>
-      </c>
-      <c r="K49" t="n">
-        <v>23</v>
-      </c>
-      <c r="L49" t="n">
-        <v>342</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -2532,12 +2136,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -2591,310 +2195,279 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Offers In Behind</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>24.47916666666667</v>
+        <v>323.75</v>
       </c>
       <c r="D2" t="n">
-        <v>14.01669154415448</v>
+        <v>105.6611404242103</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="F2" t="n">
-        <v>12.75</v>
+        <v>237.25</v>
       </c>
       <c r="G2" t="n">
-        <v>24.5</v>
+        <v>300</v>
       </c>
       <c r="H2" t="n">
-        <v>36.25</v>
+        <v>409</v>
       </c>
       <c r="I2" t="n">
-        <v>48</v>
+        <v>617</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Offers In Behind</t>
+          <t>Offers In Between</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>323.75</v>
+        <v>440.9583333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>105.6611404242103</v>
+        <v>123.0415875608875</v>
       </c>
       <c r="E3" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F3" t="n">
-        <v>237.25</v>
+        <v>363.5</v>
       </c>
       <c r="G3" t="n">
-        <v>300</v>
+        <v>427.5</v>
       </c>
       <c r="H3" t="n">
-        <v>409</v>
+        <v>521.5</v>
       </c>
       <c r="I3" t="n">
-        <v>617</v>
+        <v>701</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Offers In Between</t>
+          <t>Offers In Front</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>440.9583333333333</v>
+        <v>379.7291666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>123.0415875608875</v>
+        <v>138.7618102442798</v>
       </c>
       <c r="E4" t="n">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="F4" t="n">
-        <v>363.5</v>
+        <v>264.75</v>
       </c>
       <c r="G4" t="n">
-        <v>427.5</v>
+        <v>353</v>
       </c>
       <c r="H4" t="n">
-        <v>521.5</v>
+        <v>476.25</v>
       </c>
       <c r="I4" t="n">
-        <v>701</v>
+        <v>727</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Offers In Front</t>
+          <t>Offers Inside Team Shape</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>379.7291666666667</v>
+        <v>623.3125</v>
       </c>
       <c r="D5" t="n">
-        <v>138.7618102442798</v>
+        <v>204.7734769488034</v>
       </c>
       <c r="E5" t="n">
-        <v>143</v>
+        <v>310</v>
       </c>
       <c r="F5" t="n">
-        <v>264.75</v>
+        <v>454.25</v>
       </c>
       <c r="G5" t="n">
-        <v>353</v>
+        <v>613</v>
       </c>
       <c r="H5" t="n">
-        <v>476.25</v>
+        <v>717.25</v>
       </c>
       <c r="I5" t="n">
-        <v>727</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Offers Inside Team Shape</t>
+          <t>Offers Outside Team Shape</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>623.3125</v>
+        <v>521.125</v>
       </c>
       <c r="D6" t="n">
-        <v>204.7734769488034</v>
+        <v>144.2069471870938</v>
       </c>
       <c r="E6" t="n">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="F6" t="n">
-        <v>454.25</v>
+        <v>414.5</v>
       </c>
       <c r="G6" t="n">
-        <v>613</v>
+        <v>515</v>
       </c>
       <c r="H6" t="n">
-        <v>717.25</v>
+        <v>612.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1050</v>
+        <v>809</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Offers Outside Team Shape</t>
+          <t>Offers To Receive</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>521.125</v>
+        <v>1144.4375</v>
       </c>
       <c r="D7" t="n">
-        <v>144.2069471870938</v>
+        <v>341.3260066551463</v>
       </c>
       <c r="E7" t="n">
-        <v>267</v>
+        <v>577</v>
       </c>
       <c r="F7" t="n">
-        <v>414.5</v>
+        <v>883.25</v>
       </c>
       <c r="G7" t="n">
-        <v>515</v>
+        <v>1147</v>
       </c>
       <c r="H7" t="n">
-        <v>612.5</v>
+        <v>1315</v>
       </c>
       <c r="I7" t="n">
-        <v>809</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Offers To Receive</t>
+          <t>Receptions Between Midfield And Defensive Line</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1144.4375</v>
+        <v>317</v>
       </c>
       <c r="D8" t="n">
-        <v>341.3260066551463</v>
+        <v>100.2989149513868</v>
       </c>
       <c r="E8" t="n">
-        <v>577</v>
+        <v>146</v>
       </c>
       <c r="F8" t="n">
-        <v>883.25</v>
+        <v>239</v>
       </c>
       <c r="G8" t="n">
-        <v>1147</v>
+        <v>309.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1315</v>
+        <v>388.25</v>
       </c>
       <c r="I8" t="n">
-        <v>1859</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Receptions Between Midfield And Defensive Line</t>
+          <t>Receptions In Behind</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>34.6875</v>
       </c>
       <c r="D9" t="n">
-        <v>100.2989149513868</v>
+        <v>15.66831230982769</v>
       </c>
       <c r="E9" t="n">
-        <v>146</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>239</v>
+        <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>309.5</v>
+        <v>32</v>
       </c>
       <c r="H9" t="n">
-        <v>388.25</v>
+        <v>46</v>
       </c>
       <c r="I9" t="n">
-        <v>550</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Receptions In Behind</t>
+          <t>Receptions Under Pressure</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>34.6875</v>
+        <v>614.8958333333334</v>
       </c>
       <c r="D10" t="n">
-        <v>15.66831230982769</v>
+        <v>155.7767414403025</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>342</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>509.75</v>
       </c>
       <c r="G10" t="n">
-        <v>32</v>
+        <v>596.5</v>
       </c>
       <c r="H10" t="n">
-        <v>46</v>
+        <v>712.25</v>
       </c>
       <c r="I10" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Receptions Under Pressure</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>48</v>
-      </c>
-      <c r="C11" t="n">
-        <v>614.8958333333334</v>
-      </c>
-      <c r="D11" t="n">
-        <v>155.7767414403025</v>
-      </c>
-      <c r="E11" t="n">
-        <v>342</v>
-      </c>
-      <c r="F11" t="n">
-        <v>509.75</v>
-      </c>
-      <c r="G11" t="n">
-        <v>596.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>712.25</v>
-      </c>
-      <c r="I11" t="n">
         <v>988</v>
       </c>
     </row>
